--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="35">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,73 +55,52 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1148 Варна пристанище</t>
-  </si>
-  <si>
-    <t>1199 Varna Car Osvoboditel</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>ТубаСпорт2</t>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>Варна Чайка</t>
+  </si>
+  <si>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>В6330РА</t>
+  </si>
+  <si>
+    <t>В8983ВР</t>
   </si>
   <si>
     <t>ТубаСпорт1</t>
   </si>
   <si>
-    <t>В6330РА</t>
-  </si>
-  <si>
-    <t>В2244РМ</t>
-  </si>
-  <si>
-    <t>78970155027722143</t>
+    <t>78970155027720717</t>
+  </si>
+  <si>
+    <t>78970155027720725</t>
   </si>
   <si>
     <t>78970155027720733</t>
   </si>
   <si>
-    <t>78970155027720717</t>
-  </si>
-  <si>
-    <t>78970155027720709</t>
-  </si>
-  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
+    <t>E GAS LPG</t>
+  </si>
+  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>13:35:00</t>
-  </si>
-  <si>
-    <t>11:41:00</t>
-  </si>
-  <si>
-    <t>11:38:00</t>
-  </si>
-  <si>
-    <t>09:51:00</t>
-  </si>
-  <si>
-    <t>3236615398 3236615398</t>
-  </si>
-  <si>
-    <t>3236669997 3236669997</t>
-  </si>
-  <si>
-    <t>3236671264 3236671264</t>
-  </si>
-  <si>
-    <t>3236672025 3236672025</t>
-  </si>
-  <si>
-    <t>3236895036 3236895036</t>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>10:11</t>
+  </si>
+  <si>
+    <t>10:14</t>
+  </si>
+  <si>
+    <t>09:00</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП СПОРТ-ВАРНА</t>
@@ -547,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -556,17 +532,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -606,321 +581,282 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46266</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46253</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2">
+        <v>41.54</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.81</v>
+      </c>
+      <c r="H2" s="1">
+        <v>75.187</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="J2" s="1">
+        <v>76.434</v>
+      </c>
+      <c r="K2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2">
+        <v>173000</v>
+      </c>
+      <c r="M2">
+        <v>254381</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="3">
+        <v>46267</v>
+      </c>
+      <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2">
+      <c r="D3" t="s">
         <v>20</v>
       </c>
-      <c r="G2" t="s">
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3">
+        <v>32.2</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H3" s="1">
+        <v>20.93</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J3" s="1">
+        <v>21.252</v>
+      </c>
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3">
+        <v>68577</v>
+      </c>
+      <c r="M3">
+        <v>158061</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="3">
+        <v>46267</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="H4" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="J4" s="1">
+        <v>16.1</v>
+      </c>
+      <c r="K4" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="I2" s="1">
-        <v>35.8</v>
-      </c>
-      <c r="J2" s="1">
-        <v>1.82</v>
-      </c>
-      <c r="K2" s="1">
-        <v>36.4</v>
-      </c>
-      <c r="L2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46254</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3">
-        <v>20</v>
-      </c>
-      <c r="G3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="I3" s="1">
-        <v>30.8</v>
-      </c>
-      <c r="J3" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="K3" s="1">
-        <v>31.4</v>
-      </c>
-      <c r="L3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46254</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="I4" s="1">
-        <v>30.8</v>
-      </c>
-      <c r="J4" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="K4" s="1">
-        <v>31.4</v>
-      </c>
-      <c r="L4" t="s">
-        <v>30</v>
+      <c r="L4">
+        <v>65877</v>
       </c>
       <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>158067</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
-        <v>46254</v>
+        <v>46268</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5">
+        <v>40</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="H5" s="1">
+        <v>63.2</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="J5" s="1">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="K5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>170024</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="7">
+        <v>50</v>
+      </c>
+      <c r="C10" s="8">
+        <v>2</v>
+      </c>
+      <c r="D10" s="9">
+        <v>1.58</v>
+      </c>
+      <c r="E10" s="7">
+        <v>79</v>
+      </c>
+      <c r="F10" s="7">
+        <v>80.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="7">
+        <v>41.54</v>
+      </c>
+      <c r="C11" s="8">
+        <v>1</v>
+      </c>
+      <c r="D11" s="9">
+        <v>1.80999</v>
+      </c>
+      <c r="E11" s="7">
+        <v>75.19</v>
+      </c>
+      <c r="F11" s="7">
+        <v>76.43000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5">
-        <v>35</v>
-      </c>
-      <c r="G5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="1">
-        <v>1.81</v>
-      </c>
-      <c r="I5" s="1">
-        <v>63.35</v>
-      </c>
-      <c r="J5" s="1">
-        <v>1.84</v>
-      </c>
-      <c r="K5" s="1">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="L5" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5">
-        <v>172520</v>
-      </c>
-      <c r="N5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="3">
-        <v>46259</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6">
-        <v>56.37</v>
-      </c>
-      <c r="G6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="I6" s="1">
-        <v>87.374</v>
-      </c>
-      <c r="J6" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="K6" s="1">
-        <v>89.065</v>
-      </c>
-      <c r="L6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M6">
-        <v>270285</v>
-      </c>
-      <c r="N6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="7">
-        <v>96.37</v>
-      </c>
-      <c r="C11" s="8">
-        <v>3</v>
-      </c>
-      <c r="D11" s="9">
-        <v>1.54585</v>
-      </c>
-      <c r="E11" s="7">
-        <v>148.97</v>
-      </c>
-      <c r="F11" s="7">
-        <v>151.86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="B12" s="7">
-        <v>55</v>
+        <v>32.2</v>
       </c>
       <c r="C12" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="9">
-        <v>1.80273</v>
+        <v>0.65</v>
       </c>
       <c r="E12" s="7">
-        <v>99.15000000000001</v>
+        <v>20.93</v>
       </c>
       <c r="F12" s="7">
-        <v>100.8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>21.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="10" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B13" s="11">
-        <v>151.37</v>
+        <v>123.74</v>
       </c>
       <c r="C13" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="11">
-        <v>248.12</v>
+        <v>175.12</v>
       </c>
       <c r="F13" s="11">
-        <v>252.66</v>
+        <v>178.18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
